--- a/Spark/Data/Simulated/Bruno/model_run/descriptive.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/descriptive.xlsx
@@ -56,10 +56,10 @@
     <t xml:space="preserve">anemo-fish</t>
   </si>
   <si>
+    <t xml:space="preserve">ant-domatia</t>
+  </si>
+  <si>
     <t xml:space="preserve">ant-EFN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ant-domatia</t>
   </si>
   <si>
     <t xml:space="preserve">dispersal</t>
@@ -455,25 +455,25 @@
         <v>9.73333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>8.13976388888889</v>
+        <v>8.86816666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.114400478536747</v>
+        <v>0.114409615844116</v>
       </c>
       <c r="I2" t="n">
-        <v>21.9863818752094</v>
+        <v>21.9881379546567</v>
       </c>
       <c r="J2" t="n">
-        <v>0.102853182227786</v>
+        <v>0.102861397238352</v>
       </c>
       <c r="K2" t="n">
-        <v>18.4928255579091</v>
+        <v>18.4943026027031</v>
       </c>
       <c r="L2" t="n">
-        <v>7.19693790784743</v>
+        <v>7.19751273615778</v>
       </c>
       <c r="M2" t="n">
-        <v>7.26198331895764</v>
+        <v>7.17879115724243</v>
       </c>
     </row>
     <row r="3">
@@ -481,40 +481,40 @@
         <v>14</v>
       </c>
       <c r="B3" t="n">
-        <v>0.380917973762537</v>
+        <v>0.56520948353265</v>
       </c>
       <c r="C3" t="n">
-        <v>44.7892271883225</v>
+        <v>17.3491044387303</v>
       </c>
       <c r="D3" t="n">
-        <v>0.26931535500252</v>
+        <v>0.294167384867255</v>
       </c>
       <c r="E3" t="n">
-        <v>89.2903225806452</v>
+        <v>13.4375</v>
       </c>
       <c r="F3" t="n">
-        <v>52.3225806451613</v>
+        <v>14.875</v>
       </c>
       <c r="G3" t="n">
-        <v>39.154811827957</v>
+        <v>13.315546875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0961211208213165</v>
+        <v>0.153959497962663</v>
       </c>
       <c r="I3" t="n">
-        <v>14.653183909683</v>
+        <v>16.8180855967157</v>
       </c>
       <c r="J3" t="n">
-        <v>0.139441408558751</v>
+        <v>0.150811654472451</v>
       </c>
       <c r="K3" t="n">
-        <v>117.169276106556</v>
+        <v>11.113313755858</v>
       </c>
       <c r="L3" t="n">
-        <v>55.0709484068096</v>
+        <v>7.30931247861734</v>
       </c>
       <c r="M3" t="n">
-        <v>39.6669001432838</v>
+        <v>7.13459555958716</v>
       </c>
     </row>
     <row r="4">
@@ -522,40 +522,40 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.56520948353265</v>
+        <v>0.380917973762537</v>
       </c>
       <c r="C4" t="n">
-        <v>17.3491044387303</v>
+        <v>44.7892271883225</v>
       </c>
       <c r="D4" t="n">
-        <v>0.294167384867255</v>
+        <v>0.26931535500252</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4375</v>
+        <v>89.2903225806452</v>
       </c>
       <c r="F4" t="n">
-        <v>14.875</v>
+        <v>52.3225806451613</v>
       </c>
       <c r="G4" t="n">
-        <v>12.1282552083333</v>
+        <v>41.4708870967742</v>
       </c>
       <c r="H4" t="n">
-        <v>0.153953734378251</v>
+        <v>0.0961248354069383</v>
       </c>
       <c r="I4" t="n">
-        <v>16.8174559995991</v>
+        <v>14.6537501796744</v>
       </c>
       <c r="J4" t="n">
-        <v>0.150806008729821</v>
+        <v>0.139446797250091</v>
       </c>
       <c r="K4" t="n">
-        <v>11.1128977209737</v>
+        <v>117.173804094834</v>
       </c>
       <c r="L4" t="n">
-        <v>7.30903884925363</v>
+        <v>55.0730766149638</v>
       </c>
       <c r="M4" t="n">
-        <v>7.50200516269987</v>
+        <v>40.6744469804774</v>
       </c>
     </row>
     <row r="5">
@@ -578,25 +578,25 @@
         <v>53.1470588235294</v>
       </c>
       <c r="G5" t="n">
-        <v>49.0234803921569</v>
+        <v>51.2105147058824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.103860533363422</v>
+        <v>0.103864192869917</v>
       </c>
       <c r="I5" t="n">
-        <v>19.9192588914841</v>
+        <v>19.9199607428509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.184150314933439</v>
+        <v>0.184156803435392</v>
       </c>
       <c r="K5" t="n">
-        <v>220.188674817763</v>
+        <v>220.196433124596</v>
       </c>
       <c r="L5" t="n">
-        <v>59.2022033074991</v>
+        <v>59.2042892860756</v>
       </c>
       <c r="M5" t="n">
-        <v>55.7163153962095</v>
+        <v>57.2003909007598</v>
       </c>
     </row>
     <row r="6">
@@ -619,25 +619,25 @@
         <v>93.9252873563218</v>
       </c>
       <c r="G6" t="n">
-        <v>84.3289595306513</v>
+        <v>88.7335201149425</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0887441665300573</v>
+        <v>0.0887447775029172</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3685089876474</v>
+        <v>14.3686079098569</v>
       </c>
       <c r="J6" t="n">
-        <v>0.109503318296362</v>
+        <v>0.109504072188794</v>
       </c>
       <c r="K6" t="n">
-        <v>1182.08901858919</v>
+        <v>1182.0971568628</v>
       </c>
       <c r="L6" t="n">
-        <v>171.455752995446</v>
+        <v>171.456933408941</v>
       </c>
       <c r="M6" t="n">
-        <v>159.199600517249</v>
+        <v>163.615863229719</v>
       </c>
     </row>
   </sheetData>
